--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104517_W7.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104517_W7.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.6929</v>
+        <v>10.6095</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8362</v>
+        <v>6.996</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8566</v>
+        <v>3.6134</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0842</v>
+        <v>4.072</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.9482</v>
+        <v>-0.9396</v>
       </c>
       <c r="I2" t="n">
-        <v>5.0323</v>
+        <v>5.0116</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7971</v>
+        <v>4.7596</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5683</v>
+        <v>-0.5795</v>
       </c>
       <c r="L2" t="n">
-        <v>5.3655</v>
+        <v>5.3391</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.713</v>
+        <v>-0.6876</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3798</v>
+        <v>-0.3601</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P2" t="n">
-        <v>4.3098</v>
+        <v>4.325</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>4.3098</v>
+        <v>4.325</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8865</v>
+        <v>0.0335</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1462</v>
+        <v>0.0575</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2598</v>
+        <v>-0.024</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.2661</v>
+        <v>10.01</v>
       </c>
       <c r="E3" t="n">
-        <v>7.3935</v>
+        <v>7.9132</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8726</v>
+        <v>2.0968</v>
       </c>
       <c r="G3" t="n">
-        <v>5.7851</v>
+        <v>5.7499</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.8381</v>
+        <v>-1.849</v>
       </c>
       <c r="I3" t="n">
-        <v>7.6232</v>
+        <v>7.5989</v>
       </c>
       <c r="J3" t="n">
-        <v>5.9785</v>
+        <v>5.9204</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.6633</v>
+        <v>-1.6902</v>
       </c>
       <c r="L3" t="n">
-        <v>7.6418</v>
+        <v>7.6106</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1935</v>
+        <v>-0.1704</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1749</v>
+        <v>-0.1588</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>3.6293</v>
+        <v>3.6421</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1995</v>
+        <v>-0.4228</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7289</v>
+        <v>-0.1375</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4706</v>
+        <v>-0.2854</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W3" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. AKOBUNDU</t>
+          <t>R. OBASOHAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6641</v>
+        <v>2.3682</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1309</v>
+        <v>-0.0357</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4668</v>
+        <v>2.4039</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1085</v>
+        <v>1.1041</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4949</v>
+        <v>0.8395</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3865</v>
+        <v>0.2646</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1661</v>
+        <v>1.3034</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9048</v>
+        <v>1.1851</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2612</v>
+        <v>0.1183</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0576</v>
+        <v>-0.1993</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4099</v>
+        <v>-0.3457</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6477000000000001</v>
+        <v>0.1463</v>
       </c>
       <c r="P4" t="n">
-        <v>2.722</v>
+        <v>2.2763</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>2.722</v>
+        <v>3.4145</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0189</v>
+        <v>-0.2382</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9648</v>
+        <v>0.4153</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0541</v>
+        <v>-0.6535</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.1853</v>
+        <v>-0.7739</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.6162</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.1853</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. OBASOHAN</t>
+          <t>K. AKOBUNDU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8106</v>
+        <v>2.2661</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3999</v>
+        <v>2.6744</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2105</v>
+        <v>-0.4083</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1316</v>
+        <v>1.1109</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8545</v>
+        <v>1.4936</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2771</v>
+        <v>-0.3827</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3568</v>
+        <v>2.1567</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2184</v>
+        <v>1.8961</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1384</v>
+        <v>0.2607</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2252</v>
+        <v>-1.0458</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3639</v>
+        <v>-0.4025</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1387</v>
+        <v>-0.6433</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2683</v>
+        <v>2.7316</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.4025</v>
+        <v>2.7316</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8181</v>
+        <v>0.6026</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0121</v>
+        <v>0.5177</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.806</v>
+        <v>0.0849</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7712</v>
+        <v>-2.1789</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6105</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1607</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3998</v>
+        <v>0.7019</v>
       </c>
       <c r="E6" t="n">
-        <v>4.004</v>
+        <v>3.1557</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.6042</v>
+        <v>-2.4538</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8067</v>
+        <v>1.8097</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.5758</v>
+        <v>-1.5686</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3825</v>
+        <v>3.3783</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1865</v>
+        <v>2.1698</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0622</v>
+        <v>0.055</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1243</v>
+        <v>2.1148</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3798</v>
+        <v>-0.3601</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.638</v>
+        <v>-1.6235</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2582</v>
+        <v>1.2634</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2075</v>
+        <v>-0.4947</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5395</v>
+        <v>0.7175</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.332</v>
+        <v>-1.2122</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3851</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4847</v>
+        <v>-0.3992</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9004</v>
+        <v>1.0619</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2389</v>
+        <v>0.2599</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6669</v>
+        <v>-1.6468</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9059</v>
+        <v>1.9067</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1278</v>
+        <v>0.117</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5786</v>
+        <v>-0.5828</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7063</v>
+        <v>0.6998</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1112</v>
+        <v>0.1429</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0884</v>
+        <v>-1.064</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1995</v>
+        <v>1.2069</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1047</v>
+        <v>-0.6458</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7179</v>
+        <v>0.8496</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.6133</v>
+        <v>-1.4954</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. OLINDE</t>
+          <t>G. GOLDEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2158</v>
+        <v>-0.9205</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2466</v>
+        <v>0.5194</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0308</v>
+        <v>-1.44</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4496</v>
+        <v>0.3128</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0204</v>
+        <v>-1.296</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4292</v>
+        <v>1.6089</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8025</v>
+        <v>1.2189</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1385</v>
+        <v>0.3997</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.9409999999999999</v>
+        <v>0.8192</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3529</v>
+        <v>-0.9061</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.159</v>
+        <v>-1.6957</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5118</v>
+        <v>0.7896</v>
       </c>
       <c r="P8" t="n">
-        <v>2.0415</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>3.4025</v>
+        <v>1.3658</v>
       </c>
       <c r="S8" t="n">
-        <v>0.924</v>
+        <v>-0.2137</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7561</v>
+        <v>0.4387</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1678</v>
+        <v>-0.6524</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.7317</v>
+        <v>-1.2472</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.8924</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. GOLDEN</t>
+          <t>L. OLINDE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5938</v>
+        <v>-0.946</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0589</v>
+        <v>-1.5483</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5349</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2984</v>
+        <v>-0.4417</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.309</v>
+        <v>-0.0065</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6073</v>
+        <v>-0.4352</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2295</v>
+        <v>-0.8159999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4085</v>
+        <v>0.1379</v>
       </c>
       <c r="L9" t="n">
-        <v>0.821</v>
+        <v>-0.9539</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9311</v>
+        <v>0.3743</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.7175</v>
+        <v>-0.1444</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7864</v>
+        <v>0.5187</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>2.0487</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>3.4145</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8656</v>
+        <v>0.1707</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1542</v>
+        <v>0.4757</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7114</v>
+        <v>-0.305</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2534</v>
+        <v>-2.7237</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2534</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8971</v>
+        <v>-1.8894</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7404</v>
+        <v>-1.8231</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1567</v>
+        <v>-0.0663</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3011</v>
+        <v>-0.302</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2741</v>
+        <v>-1.2779</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9729</v>
+        <v>0.9758</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2519</v>
+        <v>0.2304</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0653</v>
+        <v>0.0442</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.553</v>
+        <v>-0.5325</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3393</v>
+        <v>-1.3221</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7864</v>
+        <v>0.7896</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1669</v>
+        <v>-0.1533</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5444</v>
+        <v>0.4991</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7114</v>
+        <v>-0.6524</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.7519</v>
+        <v>-6.3954</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.0495</v>
+        <v>-6.7139</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2976</v>
+        <v>0.3184</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.1822</v>
+        <v>-5.1968</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.7343</v>
+        <v>-4.736</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4479</v>
+        <v>-0.4609</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.9597</v>
+        <v>-4.9947</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.5681</v>
+        <v>-3.5862</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3915</v>
+        <v>-1.4084</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2225</v>
+        <v>-0.2022</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1662</v>
+        <v>-1.1497</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9436</v>
+        <v>0.9476</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6623</v>
+        <v>-0.2881</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4053</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0676</v>
+        <v>-1.0728</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>15.76000000000001</v>
+        <v>16.46720000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>10.354</v>
+        <v>10.7385</v>
       </c>
       <c r="F12" t="n">
-        <v>5.405899999999999</v>
+        <v>5.728300000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>8.520499999999998</v>
+        <v>8.4788</v>
       </c>
       <c r="H12" t="n">
-        <v>-11.0174</v>
+        <v>-10.9873</v>
       </c>
       <c r="I12" t="n">
-        <v>19.5376</v>
+        <v>19.466</v>
       </c>
       <c r="J12" t="n">
-        <v>12.332</v>
+        <v>12.0655</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.5806</v>
+        <v>-2.7207</v>
       </c>
       <c r="L12" t="n">
-        <v>14.9126</v>
+        <v>14.7864</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.8116</v>
+        <v>-3.5868</v>
       </c>
       <c r="N12" t="n">
-        <v>-8.4369</v>
+        <v>-8.266499999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>4.6252</v>
+        <v>4.6797</v>
       </c>
       <c r="P12" t="n">
-        <v>12.4757</v>
+        <v>12.5196</v>
       </c>
       <c r="Q12" t="n">
-        <v>-13.6101</v>
+        <v>-13.658</v>
       </c>
       <c r="R12" t="n">
-        <v>26.0857</v>
+        <v>26.1777</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.3438</v>
+        <v>-1.6498</v>
       </c>
       <c r="T12" t="n">
-        <v>3.8866</v>
+        <v>4.6184</v>
       </c>
       <c r="U12" t="n">
-        <v>-6.230600000000001</v>
+        <v>-6.2682</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
       <c r="W12" t="n">
-        <v>7.7452</v>
+        <v>7.7126</v>
       </c>
       <c r="X12" t="n">
-        <v>-10.6376</v>
+        <v>-10.594</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.5264</v>
+        <v>3.4094</v>
       </c>
       <c r="E13" t="n">
-        <v>7.3469</v>
+        <v>6.2646</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.8206</v>
+        <v>-2.8552</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5864</v>
+        <v>2.5856</v>
       </c>
       <c r="H13" t="n">
-        <v>5.2785</v>
+        <v>5.268</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.6921</v>
+        <v>-2.6824</v>
       </c>
       <c r="J13" t="n">
-        <v>4.6089</v>
+        <v>4.5878</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5716</v>
+        <v>4.5505</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.0225</v>
+        <v>-2.0022</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7069</v>
+        <v>0.7174</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.7294</v>
+        <v>-2.7196</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S13" t="n">
-        <v>2.21</v>
+        <v>1.0905</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8721</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3378</v>
+        <v>0.2755</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.27</v>
+        <v>-0.2667</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.3627</v>
+        <v>-1.3562</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9126</v>
+        <v>2.9487</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0038</v>
+        <v>2.0456</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.903</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4187</v>
+        <v>2.4246</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1818</v>
+        <v>1.1805</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2369</v>
+        <v>1.2442</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9595</v>
+        <v>1.9505</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9222</v>
+        <v>1.9133</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4592</v>
+        <v>0.4741</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O14" t="n">
-        <v>1.1995</v>
+        <v>1.2069</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4278</v>
+        <v>0.4542</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3126</v>
+        <v>0.3714</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1152</v>
+        <v>0.0827</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9646</v>
+        <v>2.8393</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7983</v>
+        <v>4.2363</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8338</v>
+        <v>-1.397</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1104</v>
+        <v>2.0915</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7924</v>
+        <v>3.7749</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.682</v>
+        <v>-1.6833</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1098</v>
+        <v>2.0739</v>
       </c>
       <c r="K15" t="n">
-        <v>3.0855</v>
+        <v>3.0574</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.9756</v>
+        <v>-0.9835</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0176</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7069</v>
+        <v>0.7174</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1322</v>
+        <v>1.0162</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5958</v>
+        <v>1.0728</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4637</v>
+        <v>-0.0567</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2833</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2071</v>
+        <v>1.7851</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4904</v>
+        <v>-0.9882</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9539</v>
+        <v>-0.9452</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1862</v>
+        <v>-0.1812</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7675999999999999</v>
+        <v>-0.764</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6577</v>
+        <v>0.6437</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2873</v>
+        <v>0.279</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3705</v>
+        <v>0.3647</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6116</v>
+        <v>-1.589</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1381</v>
+        <v>-1.1287</v>
       </c>
       <c r="P16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0348</v>
+        <v>1.0301</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4567</v>
+        <v>1.0519</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4915</v>
+        <v>-0.0218</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6556</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="17">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.6069</v>
+        <v>-1.3658</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0439</v>
+        <v>-0.4265</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.563</v>
+        <v>-0.9393</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.5082</v>
+        <v>-2.5039</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.1373</v>
+        <v>-3.1356</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9525</v>
+        <v>-0.9742</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7721</v>
+        <v>0.7617</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.7247</v>
+        <v>-1.7359</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5557</v>
+        <v>-1.5296</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4126</v>
+        <v>-1.3997</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1252</v>
+        <v>0.1184</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0162</v>
+        <v>0.6663</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1414</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9064</v>
+        <v>-1.5848</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8461</v>
+        <v>-1.7348</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0603</v>
+        <v>0.15</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7353</v>
+        <v>-0.7175</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2105</v>
+        <v>1.2201</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.9458</v>
+        <v>-1.9376</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2105</v>
+        <v>0.2096</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1732</v>
+        <v>0.1724</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9458</v>
+        <v>-0.9271</v>
       </c>
       <c r="N18" t="n">
-        <v>1.0373</v>
+        <v>1.0477</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.9831</v>
+        <v>-1.9749</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7528</v>
+        <v>1.0627</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4386</v>
+        <v>0.5596</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3142</v>
+        <v>0.5032</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="19">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1015</v>
+        <v>-1.6375</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4597</v>
+        <v>-1.3612</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6417</v>
+        <v>-0.2763</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6721</v>
+        <v>-0.6689000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7432</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4153</v>
+        <v>-1.4073</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2309</v>
+        <v>0.2161</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1936</v>
+        <v>0.1789</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.903</v>
+        <v>-0.8851</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5496</v>
+        <v>0.5595</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0684</v>
+        <v>0.3973</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5777</v>
+        <v>0.699</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.646</v>
+        <v>-0.3017</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3441</v>
+        <v>-2.6732</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6952</v>
+        <v>-2.8379</v>
       </c>
       <c r="F20" t="n">
-        <v>0.351</v>
+        <v>0.1648</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4004</v>
+        <v>-1.3809</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3693</v>
+        <v>0.3732</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7698</v>
+        <v>-1.7541</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5457</v>
+        <v>-0.5568</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6203</v>
+        <v>-0.6313</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8548</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>0.9896</v>
+        <v>1.0044</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.8444</v>
+        <v>-1.8285</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4588</v>
+        <v>0.1222</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1603</v>
+        <v>0.0439</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2985</v>
+        <v>0.0784</v>
       </c>
       <c r="V20" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.744</v>
+        <v>-2.8749</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5877</v>
+        <v>-2.9614</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1563</v>
+        <v>0.0866</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6036</v>
+        <v>-0.5929</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5959</v>
+        <v>0.6</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1994</v>
+        <v>-1.1929</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4458</v>
+        <v>0.4369</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1949</v>
+        <v>1.1893</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0494</v>
+        <v>-1.0298</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3548</v>
+        <v>0.2219</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5958</v>
+        <v>0.2437</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2411</v>
+        <v>-0.0218</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. AGADA</t>
+          <t>K. ZORIKS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8737</v>
+        <v>-3.6028</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0499</v>
+        <v>-4.195</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8238</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8024</v>
+        <v>-3.3065</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1627</v>
+        <v>-0.5343</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6397</v>
+        <v>-2.7722</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5484</v>
+        <v>-3.2387</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3819</v>
+        <v>-0.907</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9302</v>
+        <v>-2.3317</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3507</v>
+        <v>-0.0678</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2192</v>
+        <v>0.3727</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5699</v>
+        <v>-0.4405</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.8562</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.9903</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3478</v>
+        <v>0.1394</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2994</v>
+        <v>0.6176</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0484</v>
+        <v>-0.4782</v>
       </c>
       <c r="V22" t="n">
-        <v>0.4371</v>
+        <v>0.7025</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>0.7025</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K. ZORIKS</t>
+          <t>C. AGADA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9162</v>
+        <v>-3.8262</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.11</v>
+        <v>-3.345</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1938</v>
+        <v>-0.4813</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.309</v>
+        <v>-0.8198</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5368000000000001</v>
+        <v>-0.1854</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.7721</v>
+        <v>-0.6343</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.2191</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.8974</v>
+        <v>-0.4147</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.3218</v>
+        <v>0.9233</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0898</v>
+        <v>-1.3284</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3605</v>
+        <v>0.2292</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4504</v>
+        <v>-1.5576</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1342</v>
+        <v>-3.8697</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-5.0079</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1801</v>
+        <v>0.4275</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3297</v>
+        <v>0.0648</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8505</v>
+        <v>0.3627</v>
       </c>
       <c r="V23" t="n">
-        <v>0.7071</v>
+        <v>0.4358</v>
       </c>
       <c r="W23" t="n">
-        <v>0.7071</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.6536999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.3873</v>
+        <v>-5.0407</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.9696</v>
+        <v>-3.1982</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4178</v>
+        <v>-1.8424</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.6509</v>
+        <v>-4.6449</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.8975</v>
+        <v>-1.8984</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.7534</v>
+        <v>-2.7465</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.2426</v>
+        <v>-2.2707</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.864</v>
+        <v>-1.883</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.3786</v>
+        <v>-0.3877</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.4083</v>
+        <v>-2.3742</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.0335</v>
+        <v>-0.0154</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.3749</v>
+        <v>-2.3588</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.9317</v>
+        <v>-0.5748</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7652</v>
+        <v>0.0624</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.1665</v>
+        <v>-0.6372</v>
       </c>
       <c r="V24" t="n">
-        <v>2.2368</v>
+        <v>2.2278</v>
       </c>
       <c r="W24" t="n">
-        <v>2.6675</v>
+        <v>2.6522</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.4307</v>
+        <v>-0.4245</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-15.7598</v>
+        <v>-12.6116</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.406000000000001</v>
+        <v>-5.728400000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.3541</v>
+        <v>-6.883100000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>-8.520300000000001</v>
+        <v>-8.4788</v>
       </c>
       <c r="H25" t="n">
-        <v>11.0175</v>
+        <v>10.9875</v>
       </c>
       <c r="I25" t="n">
-        <v>-19.5376</v>
+        <v>-19.466</v>
       </c>
       <c r="J25" t="n">
-        <v>3.811599999999999</v>
+        <v>3.586700000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>8.4368</v>
+        <v>8.266500000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>-4.6252</v>
+        <v>-4.6799</v>
       </c>
       <c r="M25" t="n">
-        <v>-12.3318</v>
+        <v>-12.0656</v>
       </c>
       <c r="N25" t="n">
-        <v>2.5805</v>
+        <v>2.7205</v>
       </c>
       <c r="O25" t="n">
-        <v>-14.9126</v>
+        <v>-14.7863</v>
       </c>
       <c r="P25" t="n">
-        <v>-12.476</v>
+        <v>-12.5197</v>
       </c>
       <c r="Q25" t="n">
-        <v>-26.0857</v>
+        <v>-26.1776</v>
       </c>
       <c r="R25" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="S25" t="n">
-        <v>2.344</v>
+        <v>5.505600000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>6.230300000000001</v>
+        <v>6.2684</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.8866</v>
+        <v>-0.7628000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>2.8925</v>
+        <v>2.8815</v>
       </c>
       <c r="W25" t="n">
-        <v>10.6378</v>
+        <v>10.5941</v>
       </c>
       <c r="X25" t="n">
-        <v>-7.7453</v>
+        <v>-7.7126</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104517_W7.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104517_W7.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104517_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104517_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104517_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104517_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104517_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104517_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104517_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104517_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104517_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104517_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-10.594</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.3562</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104517_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104517_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104517_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104517_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104517_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104517_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104517_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104517_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104517_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104517_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.6536999999999999</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104517_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.4245</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104517_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-7.7126</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
